--- a/家庭服务机器人_竞品对标与定价测算模板.xlsx
+++ b/家庭服务机器人_竞品对标与定价测算模板.xlsx
@@ -862,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>待核实（官网/发布会）</t>
+          <t>—（官网未公开，引用前需核实）</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1447,53 +1447,17 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>（自选补充：建议 1X/Figure 等海外厂商）</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>（自选补充）</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="5" t="inlineStr">
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>使用规则：① 每一格都要能回答“你在哪看到的”——来源列必须给链接/媒体名+核实日期；② 价格写“口径”（买断/租金/单次/补贴价）不写裸数字；③ “我的判断”列是整张表的灵魂：不是复述事实，而是说出这对目标公司意味着什么。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="5" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>查价提示：电商价随促销波动，写“官方指导价 + 到手价”两个口径；二手价去闲鱼看，是真实支付意愿。前 8 行已按 2026-09-05 核实的公开信息填好，引用前自行复核。</t>
         </is>
@@ -1501,9 +1465,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="B16:M16"/>
     <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="B18:M18"/>
+    <mergeCell ref="B15:M15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
